--- a/Assets/Configs/TileBlocks.xlsx
+++ b/Assets/Configs/TileBlocks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17820CCD-491F-415E-81A8-464C0154A0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A554F13-6E45-4E59-98DA-84A7ACDDF060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="9970"/>
+    <workbookView xWindow="-21450" yWindow="1630" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TileBlocks" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>TileSpriteName</t>
   </si>
@@ -82,12 +82,20 @@
   </si>
   <si>
     <t>GO_Wall_03</t>
+  </si>
+  <si>
+    <t>Wall_DishOutlet</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Wall_DishOutlet</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1032,11 +1040,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1058,7 +1066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1069,7 +1077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1080,7 +1088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1091,7 +1099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1102,7 +1110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1113,7 +1121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1124,7 +1132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1132,7 +1140,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1140,16 +1148,25 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Configs/TileBlocks.xlsx
+++ b/Assets/Configs/TileBlocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A554F13-6E45-4E59-98DA-84A7ACDDF060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E67D71-6E87-4B2E-AB8C-AEE24E324EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21450" yWindow="1630" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>TileSpriteName</t>
   </si>
@@ -69,19 +69,10 @@
     <t>Wall_1</t>
   </si>
   <si>
-    <t>GO_Wall_01</t>
-  </si>
-  <si>
     <t>Wall_2</t>
   </si>
   <si>
-    <t>GO_Wall_02</t>
-  </si>
-  <si>
     <t>Wall_3</t>
-  </si>
-  <si>
-    <t>GO_Wall_03</t>
   </si>
   <si>
     <t>Wall_DishOutlet</t>
@@ -90,6 +81,29 @@
   <si>
     <t>GO_Wall_DishOutlet</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall_4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_1</t>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_2</t>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_3</t>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_4</t>
+  </si>
+  <si>
+    <t>Wall_TowerRoot</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Wall_TowerRoot</t>
   </si>
 </sst>
 </file>
@@ -1041,10 +1055,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1055,7 +1072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1066,7 +1083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1077,7 +1094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1088,7 +1105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1099,7 +1116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1121,7 +1138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1132,41 +1149,57 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B14" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Configs/TileBlocks.xlsx
+++ b/Assets/Configs/TileBlocks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E67D71-6E87-4B2E-AB8C-AEE24E324EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F107B1-15DC-43BB-860B-820550942C65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21450" yWindow="1630" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>TileSpriteName</t>
   </si>
@@ -104,6 +104,22 @@
   </si>
   <si>
     <t>GO_Wall_TowerRoot</t>
+  </si>
+  <si>
+    <t>Wall_5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Wall_Chef_6</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall_6</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1055,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.33203125" customWidth="1"/>
@@ -1183,17 +1199,33 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
